--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.01_Q80_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.01_Q80_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.000523517198494938</v>
+        <v>0.0002352196808452669</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000523517198494938</v>
+        <v>0.0002352196808452669</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0009812011779143197</v>
+        <v>0.000454014530945484</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009812011779143197</v>
+        <v>0.000454014530945484</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.002048028079378936</v>
+        <v>0.0009445277166405057</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002048028079378936</v>
+        <v>0.0009445277166405057</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.003428346807783958</v>
+        <v>0.00158506875956366</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003428346807783958</v>
+        <v>0.00158506875956366</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.004106233739766757</v>
+        <v>0.001899022812087024</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004106233739766757</v>
+        <v>0.001899022812087024</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.003956014373626137</v>
+        <v>0.001825900515383961</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003956014373626137</v>
+        <v>0.001825900515383961</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.003521301344594086</v>
+        <v>0.001626565435970797</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003521301344594086</v>
+        <v>0.001626565435970797</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.003197850729485737</v>
+        <v>0.001479332279659877</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003197850729485737</v>
+        <v>0.001479332279659877</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.003105561580469395</v>
+        <v>0.001438699439333064</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003105561580469395</v>
+        <v>0.001438699439333064</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.002781799812374784</v>
+        <v>0.001288799791663003</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002781799812374784</v>
+        <v>0.001288799791663003</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
